--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E4A032-5CC0-42E9-B4FA-110C8A8D8C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599586E-5073-483F-9FF4-5A697BAE0AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -89,30 +89,9 @@
     <t>IsAdvancePermitted__c</t>
   </si>
   <si>
-    <t>AnnouncementDescription__c</t>
-  </si>
-  <si>
-    <t>EligibleApplicantTypes__c</t>
-  </si>
-  <si>
-    <t>State governments;Independent school districts</t>
-  </si>
-  <si>
     <t>Financials</t>
   </si>
   <si>
-    <t>AwardFloor__c</t>
-  </si>
-  <si>
-    <t>AwardCeiling__c</t>
-  </si>
-  <si>
-    <t>EstimatedNumberOfAwards__c</t>
-  </si>
-  <si>
-    <t>TotalCommittedAmount__c</t>
-  </si>
-  <si>
     <t>fieldProjectAbstract__c</t>
   </si>
   <si>
@@ -459,13 +438,40 @@
   </si>
   <si>
     <t>GMS Administrator</t>
+  </si>
+  <si>
+    <t>fieldAllocationlevel__c</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>fieldEligibleApplicantTypes__c</t>
+  </si>
+  <si>
+    <t>fieldAwardFloor__c</t>
+  </si>
+  <si>
+    <t>fieldAwardCeiling__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>fieldTotalCommittedAmount__c</t>
+  </si>
+  <si>
+    <t>fieldAnnouncementDescription__c</t>
+  </si>
+  <si>
+    <t>State Governments;Individuals;School District</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,6 +499,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -515,7 +527,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -531,6 +543,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -835,10 +848,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -846,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -857,10 +870,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -868,7 +881,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -879,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -890,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -927,10 +940,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -938,54 +951,54 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1013,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1014,10 +1027,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1025,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1061,10 +1074,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1072,10 +1085,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1083,10 +1096,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1094,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1105,10 +1118,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1116,10 +1129,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1127,10 +1140,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1138,10 +1151,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1149,10 +1162,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1160,10 +1173,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1171,10 +1184,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1207,10 +1220,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1218,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1229,10 +1242,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1240,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1277,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1288,10 +1301,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1299,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1310,7 +1323,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1321,10 +1334,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1332,10 +1345,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1343,10 +1356,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1424,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -1468,7 +1481,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
@@ -1479,7 +1492,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -1515,10 +1528,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1526,10 +1539,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1537,10 +1550,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1548,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C5">
         <v>1234</v>
@@ -1556,10 +1569,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>330</v>
@@ -1595,10 +1608,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1606,10 +1619,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1617,10 +1630,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1653,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C2">
         <v>365</v>
@@ -1664,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C3">
         <v>455</v>
@@ -1675,10 +1688,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1686,10 +1699,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1697,10 +1710,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1708,10 +1721,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1719,10 +1732,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1755,10 +1768,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1766,10 +1779,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1777,10 +1790,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1788,10 +1801,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1799,10 +1812,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1810,10 +1823,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1821,10 +1834,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1832,10 +1845,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1843,10 +1856,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1880,10 +1893,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1891,7 +1904,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1902,10 +1915,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1913,7 +1926,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -1924,7 +1937,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -1935,7 +1948,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -1971,10 +1984,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1982,10 +1995,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1993,10 +2006,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2059,10 +2072,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2070,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -2081,10 +2094,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2092,7 +2105,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -2103,7 +2116,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -2114,7 +2127,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -2151,7 +2164,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2162,7 +2175,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>1825</v>
@@ -2173,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2205,7 +2218,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2216,7 +2229,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>1825</v>
@@ -2252,10 +2265,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2263,10 +2276,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2274,7 +2287,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -2312,10 +2325,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2323,7 +2336,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -2336,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B47C19A-7081-4532-8CD1-2D1BC531686A}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
@@ -2359,7 +2372,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -2370,7 +2383,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -2381,7 +2394,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -2392,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -2403,7 +2416,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -2414,7 +2427,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -2425,7 +2438,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -2436,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -2447,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
@@ -2458,7 +2471,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -2469,10 +2482,21 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2504,8 +2528,8 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
+      <c r="B2" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2515,11 +2539,11 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
+      <c r="B3" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2527,18 +2551,18 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2546,10 +2570,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2557,10 +2581,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2568,10 +2592,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599586E-5073-483F-9FF4-5A697BAE0AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A59948-1D0C-456B-88A3-F11A7B1638F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="145">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -404,12 +404,6 @@
     <t>fieldSvProgramFormQ9__c</t>
   </si>
   <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>CalReportingEndDate__c</t>
-  </si>
-  <si>
     <t>Automation Direct Grant</t>
   </si>
   <si>
@@ -465,6 +459,21 @@
   </si>
   <si>
     <t>State Governments;Individuals;School District</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>fieldGrantType__c</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>fieldAllocationLevel__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -1253,7 +1262,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1293,7 +1302,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1359,7 +1368,7 @@
         <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1370,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEB37B-B28E-4F60-BECB-CD35E74B4C36}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.88671875" bestFit="1" customWidth="1"/>
@@ -1496,6 +1505,28 @@
       </c>
       <c r="C11" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1896,7 +1927,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1984,10 +2015,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1995,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2006,10 +2037,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2075,7 +2106,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2097,7 +2128,7 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2493,10 +2524,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2529,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2540,10 +2571,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2562,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2573,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2584,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2595,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A59948-1D0C-456B-88A3-F11A7B1638F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E77341-9701-4143-8CB8-B8396411EFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="148">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -236,12 +236,6 @@
     <t>Children’s Health Insurance Program</t>
   </si>
   <si>
-    <t>Test Descrption</t>
-  </si>
-  <si>
-    <t>fieldObjectives__c</t>
-  </si>
-  <si>
     <t>fieldAnnouncementName__c</t>
   </si>
   <si>
@@ -474,6 +468,21 @@
   </si>
   <si>
     <t>fieldCalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>Abbreviation__c</t>
+  </si>
+  <si>
+    <t>PREG</t>
+  </si>
+  <si>
+    <t>WebsiteAddress__c</t>
+  </si>
+  <si>
+    <t>http://automate.com</t>
+  </si>
+  <si>
+    <t>Objectives__c</t>
   </si>
 </sst>
 </file>
@@ -835,13 +844,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9504DEE-61CE-471E-847C-6DA763CE3AF2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -863,7 +872,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -874,7 +883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -885,7 +894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -896,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -907,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -927,13 +936,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531E32A4-7E13-4409-95B5-698B0506DEBB}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,7 +953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -955,7 +964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -966,7 +975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -977,7 +986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -988,7 +997,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -999,7 +1008,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1018,11 +1027,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5034D7D-3DCC-4A67-A25F-FCA9FE48CDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1031,23 +1040,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1061,13 +1070,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70638D0A-5B68-4E82-8E59-C902079F733A}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1089,111 +1098,111 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -1207,13 +1216,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88D2545-36F8-47CF-B9C1-1EF7F48C6F22}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,45 +1233,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1277,13 +1286,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CB8E10-5A8B-4AF3-AF66-F1E9AA7C9BBC}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1302,54 +1311,54 @@
         <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1357,18 +1366,18 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1380,13 +1389,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEB37B-B28E-4F60-BECB-CD35E74B4C36}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1419,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1430,7 +1439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1441,7 +1450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1452,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1463,7 +1472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1474,7 +1483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1496,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1507,26 +1516,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>141</v>
       </c>
-      <c r="C12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>143</v>
-      </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1537,13 +1546,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82865F4C-F847-4F90-8B11-C831BFCC23C2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,56 +1563,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C5">
         <v>1234</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>330</v>
@@ -1617,13 +1626,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDAC24B-DC90-49E6-BD31-6F210026CA6D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1634,34 +1643,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
@@ -1675,13 +1684,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F7845C-214C-4C02-A5F4-6F38FB46E35D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1692,29 +1701,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1725,7 +1734,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1745,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1747,7 +1756,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1758,7 +1767,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1777,13 +1786,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE64D93B-66B6-48F6-99BC-E4BA23590E06}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1794,103 +1803,103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1901,14 +1910,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9414A1A-FB8B-4B66-A538-3949CB53646C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1919,7 +1928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1927,10 +1936,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1941,7 +1950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1952,7 +1961,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1963,7 +1972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1974,7 +1983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1993,13 +2002,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC7C533-9694-4FF8-A93E-689ECBD164CC}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2010,65 +2019,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2081,13 +2090,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E83D430-2DDF-4C96-A733-8F6A18593E6C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2098,7 +2107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2106,10 +2115,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2120,7 +2129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2128,10 +2137,10 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2142,7 +2151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2153,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2173,13 +2182,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03E8B95-40CB-49F7-AF29-3A2B27B21A61}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2190,40 +2199,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>66</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{0A50B6A7-28E4-439C-ADC5-CDEB6D17181D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2231,9 +2243,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C485CB82-74B9-4E1E-9CE3-715999920922}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2244,7 +2256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2255,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2274,13 +2286,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19EA7F8-0885-4456-A6E5-96AB05BF51FA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2291,18 +2303,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2313,12 +2325,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -2333,14 +2345,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0E25E5-8973-4E31-A3CE-0B2930FA70C8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2351,23 +2363,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -2381,13 +2393,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B47C19A-7081-4532-8CD1-2D1BC531686A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2398,62 +2410,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2486,48 +2498,48 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2538,13 +2550,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BADE6FB-E965-4263-BE22-5F02F8843366}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2555,29 +2567,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2588,45 +2600,45 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A59948-1D0C-456B-88A3-F11A7B1638F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB446306-5B87-42E0-AD8E-3F17C618DCEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="145">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -835,13 +835,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9504DEE-61CE-471E-847C-6DA763CE3AF2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -863,7 +863,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -874,7 +874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -885,7 +885,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -907,7 +907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -927,13 +927,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531E32A4-7E13-4409-95B5-698B0506DEBB}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,7 +944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -955,7 +955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -966,7 +966,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -977,7 +977,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -988,7 +988,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -999,7 +999,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1018,9 +1018,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5034D7D-3DCC-4A67-A25F-FCA9FE48CDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1061,13 +1061,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70638D0A-5B68-4E82-8E59-C902079F733A}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1207,13 +1207,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88D2545-36F8-47CF-B9C1-1EF7F48C6F22}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
+    <col min="3" max="3" width="33.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1277,13 +1277,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CB8E10-5A8B-4AF3-AF66-F1E9AA7C9BBC}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1380,13 +1380,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEB37B-B28E-4F60-BECB-CD35E74B4C36}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1537,13 +1537,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82865F4C-F847-4F90-8B11-C831BFCC23C2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1617,13 +1617,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDAC24B-DC90-49E6-BD31-6F210026CA6D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1675,13 +1675,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F7845C-214C-4C02-A5F4-6F38FB46E35D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1777,13 +1777,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE64D93B-66B6-48F6-99BC-E4BA23590E06}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1901,14 +1901,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9414A1A-FB8B-4B66-A538-3949CB53646C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1993,13 +1993,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC7C533-9694-4FF8-A93E-689ECBD164CC}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2043,32 +2043,32 @@
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2081,13 +2081,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E83D430-2DDF-4C96-A733-8F6A18593E6C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2172,14 +2172,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03E8B95-40CB-49F7-AF29-3A2B27B21A61}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2190,36 +2190,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2231,9 +2209,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C485CB82-74B9-4E1E-9CE3-715999920922}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2244,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2255,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2274,13 +2252,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19EA7F8-0885-4456-A6E5-96AB05BF51FA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2291,7 +2269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2302,7 +2280,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2313,7 +2291,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2333,14 +2311,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0E25E5-8973-4E31-A3CE-0B2930FA70C8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2351,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2362,7 +2340,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2381,13 +2359,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B47C19A-7081-4532-8CD1-2D1BC531686A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2398,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2409,7 +2387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2420,7 +2398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2431,7 +2409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2442,7 +2420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2486,7 +2464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2497,7 +2475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2508,7 +2486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2519,7 +2497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2538,13 +2516,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BADE6FB-E965-4263-BE22-5F02F8843366}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2555,7 +2533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2577,7 +2555,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2588,7 +2566,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2599,7 +2577,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2610,7 +2588,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2621,7 +2599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91697267-8FEF-4FFE-A504-83490596D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7870BE-835F-47EA-90A0-556A7D4AA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="152">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -401,9 +401,6 @@
     <t>Automation Direct Grant</t>
   </si>
   <si>
-    <t>Automation Program For Test</t>
-  </si>
-  <si>
     <t>Automation Program For Announcement</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
     <t>Program Manager</t>
   </si>
   <si>
-    <t>GMS Administrator</t>
-  </si>
-  <si>
     <t>fieldAllocationlevel__c</t>
   </si>
   <si>
@@ -483,6 +477,24 @@
   </si>
   <si>
     <t>Objectives__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>PrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -545,7 +557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -562,6 +574,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1271,7 +1289,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1377,7 +1395,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1521,10 +1539,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1532,10 +1550,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1936,7 +1954,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2024,10 +2042,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2035,10 +2053,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2046,10 +2064,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2097,85 +2115,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C2" t="s">
-        <v>120</v>
+      <c r="C2" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>128</v>
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
+      <c r="A7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" tooltip="https://test7-internal.my.salesforce.com/00e0b000001fm3y" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{8D7FE799-8783-40F7-87C7-3B66C044DD34}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2204,10 +2225,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2215,10 +2236,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2226,7 +2247,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2536,10 +2557,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2572,7 +2593,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2583,10 +2604,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2605,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2616,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2627,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2638,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7870BE-835F-47EA-90A0-556A7D4AA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA78E93A-2482-45BC-9244-A3877E13C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="151">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -492,9 +492,6 @@
   </si>
   <si>
     <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2163,7 @@
         <v>150</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2177,7 +2174,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2188,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA78E93A-2482-45BC-9244-A3877E13C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91697267-8FEF-4FFE-A504-83490596D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="148">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -401,6 +401,9 @@
     <t>Automation Direct Grant</t>
   </si>
   <si>
+    <t>Automation Program For Test</t>
+  </si>
+  <si>
     <t>Automation Program For Announcement</t>
   </si>
   <si>
@@ -422,6 +425,9 @@
     <t>Program Manager</t>
   </si>
   <si>
+    <t>GMS Administrator</t>
+  </si>
+  <si>
     <t>fieldAllocationlevel__c</t>
   </si>
   <si>
@@ -477,21 +483,6 @@
   </si>
   <si>
     <t>Objectives__c</t>
-  </si>
-  <si>
-    <t>Automation Runtime Internal Program</t>
-  </si>
-  <si>
-    <t>Type__c</t>
-  </si>
-  <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
   </si>
 </sst>
 </file>
@@ -554,7 +545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -571,12 +562,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1286,7 +1271,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1392,7 +1377,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1536,10 +1521,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1547,10 +1532,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +1936,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2039,10 +2024,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2050,10 +2035,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2061,10 +2046,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2112,88 +2097,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>146</v>
+      <c r="C2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>149</v>
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" tooltip="https://test7-internal.my.salesforce.com/00e0b000001fm3y" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{8D7FE799-8783-40F7-87C7-3B66C044DD34}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2222,10 +2204,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2233,10 +2215,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2244,7 +2226,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2554,10 +2536,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2590,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2601,10 +2583,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2623,7 +2605,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2634,7 +2616,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2645,7 +2627,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2656,7 +2638,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91697267-8FEF-4FFE-A504-83490596D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36FE289-D1D5-4B08-A72D-8E0DF908A239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="150">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -401,9 +401,6 @@
     <t>Automation Direct Grant</t>
   </si>
   <si>
-    <t>Automation Program For Test</t>
-  </si>
-  <si>
     <t>Automation Program For Announcement</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
     <t>Program Manager</t>
   </si>
   <si>
-    <t>GMS Administrator</t>
-  </si>
-  <si>
     <t>fieldAllocationlevel__c</t>
   </si>
   <si>
@@ -483,6 +477,18 @@
   </si>
   <si>
     <t>Objectives__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>PrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1277,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1377,7 +1383,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1521,10 +1527,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1532,10 +1538,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1936,7 +1942,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2024,10 +2030,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2035,10 +2041,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2046,10 +2052,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2115,7 +2121,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2123,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -2134,10 +2140,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>128</v>
+        <v>148</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2174,8 +2180,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{E26A2D75-46D0-4520-B792-0F38F1D77E43}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2204,10 +2213,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2215,10 +2224,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2226,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2536,10 +2545,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2572,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2583,10 +2592,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2605,7 +2614,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2616,7 +2625,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2627,7 +2636,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2638,7 +2647,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F844F-2DEF-4D95-AD0E-58713696AF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E0648A-B099-4F0D-95E1-E7FFB35D420E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="151">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -492,9 +492,6 @@
   </si>
   <si>
     <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -862,13 +859,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9504DEE-61CE-471E-847C-6DA763CE3AF2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -890,7 +887,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -901,7 +898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -912,7 +909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -923,7 +920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -934,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -954,13 +951,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531E32A4-7E13-4409-95B5-698B0506DEBB}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -982,7 +979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -993,7 +990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1004,7 +1001,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1015,7 +1012,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1026,7 +1023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1045,9 +1042,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5034D7D-3DCC-4A67-A25F-FCA9FE48CDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>76</v>
       </c>
@@ -1058,7 +1055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1069,7 +1066,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1088,13 +1085,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70638D0A-5B68-4E82-8E59-C902079F733A}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1116,7 +1113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1127,7 +1124,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1135,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1146,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1160,7 +1157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1171,7 +1168,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1193,7 +1190,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1204,7 +1201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1215,7 +1212,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1234,13 +1231,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88D2545-36F8-47CF-B9C1-1EF7F48C6F22}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
+    <col min="3" max="3" width="33.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1262,7 +1259,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1273,7 +1270,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1281,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1304,13 +1301,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CB8E10-5A8B-4AF3-AF66-F1E9AA7C9BBC}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1332,7 +1329,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1343,7 +1340,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1354,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1365,7 +1362,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1376,7 +1373,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1384,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1407,13 +1404,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEB37B-B28E-4F60-BECB-CD35E74B4C36}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +1421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1435,7 +1432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1457,7 +1454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1479,7 +1476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1501,7 +1498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1512,7 +1509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1534,7 +1531,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1545,7 +1542,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1564,13 +1561,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82865F4C-F847-4F90-8B11-C831BFCC23C2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1592,7 +1589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1603,7 +1600,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1614,7 +1611,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1625,7 +1622,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1644,13 +1641,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDAC24B-DC90-49E6-BD31-6F210026CA6D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1661,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1672,7 +1669,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +1680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1702,13 +1699,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F7845C-214C-4C02-A5F4-6F38FB46E35D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1730,7 +1727,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1752,7 +1749,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1763,7 +1760,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1774,7 +1771,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1785,7 +1782,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1804,13 +1801,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE64D93B-66B6-48F6-99BC-E4BA23590E06}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1821,7 +1818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1832,7 +1829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1843,7 +1840,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1854,7 +1851,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1865,7 +1862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1876,7 +1873,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1887,7 +1884,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1898,7 +1895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1909,7 +1906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1928,14 +1925,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9414A1A-FB8B-4B66-A538-3949CB53646C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1946,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1957,7 +1954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1968,7 +1965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1979,7 +1976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1990,7 +1987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2001,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2020,13 +2017,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC7C533-9694-4FF8-A93E-689ECBD164CC}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2037,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2048,7 +2045,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2059,7 +2056,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2070,32 +2067,32 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2108,13 +2105,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E83D430-2DDF-4C96-A733-8F6A18593E6C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -2136,7 +2133,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -2147,7 +2144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2158,7 +2155,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -2166,10 +2163,10 @@
         <v>150</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -2177,10 +2174,10 @@
         <v>8</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
@@ -2188,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2203,13 +2200,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03E8B95-40CB-49F7-AF29-3A2B27B21A61}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2220,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2231,7 +2228,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2242,7 +2239,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2264,9 +2261,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C485CB82-74B9-4E1E-9CE3-715999920922}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2277,7 +2274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2288,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2307,13 +2304,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19EA7F8-0885-4456-A6E5-96AB05BF51FA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2324,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2335,7 +2332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2346,7 +2343,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2366,14 +2363,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0E25E5-8973-4E31-A3CE-0B2930FA70C8}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2384,7 +2381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2395,7 +2392,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2414,13 +2411,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B47C19A-7081-4532-8CD1-2D1BC531686A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2442,7 +2439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2486,7 +2483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2497,7 +2494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2508,7 +2505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2519,7 +2516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2552,7 +2549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2571,13 +2568,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BADE6FB-E965-4263-BE22-5F02F8843366}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2599,7 +2596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2610,7 +2607,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2632,7 +2629,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2643,7 +2640,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2654,7 +2651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -3,31 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E0648A-B099-4F0D-95E1-E7FFB35D420E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2987F7-DF88-4F96-B652-EE42963446B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
     <sheet name="ProgramCreation_v_for_Ann" sheetId="40" r:id="rId2"/>
     <sheet name="ProgramCreation_v" sheetId="22" r:id="rId3"/>
-    <sheet name="ProgramEdition_v" sheetId="23" r:id="rId4"/>
-    <sheet name="ProgramEditon_forCkEditor" sheetId="37" r:id="rId5"/>
-    <sheet name="NewOrgAnnCreation_v" sheetId="24" r:id="rId6"/>
-    <sheet name="QA_OrgAnnCreation" sheetId="38" r:id="rId7"/>
-    <sheet name="NewOrg2ndModal_v" sheetId="25" r:id="rId8"/>
-    <sheet name="NewOrgAnnEdition_v" sheetId="26" r:id="rId9"/>
-    <sheet name="NewOrgAppEddition_v" sheetId="27" r:id="rId10"/>
-    <sheet name="StandardAssurancesForm_v" sheetId="28" r:id="rId11"/>
-    <sheet name="ProgramApplicationForm_v" sheetId="29" r:id="rId12"/>
-    <sheet name="PaymentRequestSchedule_v" sheetId="30" r:id="rId13"/>
-    <sheet name="GrantCreation_v" sheetId="31" r:id="rId14"/>
-    <sheet name="Grant_Edition_v" sheetId="32" r:id="rId15"/>
-    <sheet name="StandAloneEdition_v" sheetId="33" r:id="rId16"/>
-    <sheet name="SiteVisitCreation_v" sheetId="34" r:id="rId17"/>
-    <sheet name="SiteVisitEdition_v" sheetId="35" r:id="rId18"/>
-    <sheet name="GeneralReviewForm_v" sheetId="36" r:id="rId19"/>
-    <sheet name="Contacts" sheetId="41" r:id="rId20"/>
+    <sheet name="ProgramCreation1_v" sheetId="42" r:id="rId4"/>
+    <sheet name="ProgramEdition_v" sheetId="23" r:id="rId5"/>
+    <sheet name="ProgramEditon_forCkEditor" sheetId="37" r:id="rId6"/>
+    <sheet name="NewOrgAnnCreation_v" sheetId="24" r:id="rId7"/>
+    <sheet name="QA_OrgAnnCreation" sheetId="38" r:id="rId8"/>
+    <sheet name="NewOrg2ndModal_v" sheetId="25" r:id="rId9"/>
+    <sheet name="NewOrgAnnEdition_v" sheetId="26" r:id="rId10"/>
+    <sheet name="NewOrgAppEddition_v" sheetId="27" r:id="rId11"/>
+    <sheet name="StandardAssurancesForm_v" sheetId="28" r:id="rId12"/>
+    <sheet name="ProgramApplicationForm_v" sheetId="29" r:id="rId13"/>
+    <sheet name="PaymentRequestSchedule_v" sheetId="30" r:id="rId14"/>
+    <sheet name="GrantCreation_v" sheetId="31" r:id="rId15"/>
+    <sheet name="Grant_Edition_v" sheetId="32" r:id="rId16"/>
+    <sheet name="StandAloneEdition_v" sheetId="33" r:id="rId17"/>
+    <sheet name="SiteVisitCreation_v" sheetId="34" r:id="rId18"/>
+    <sheet name="SiteVisitEdition_v" sheetId="35" r:id="rId19"/>
+    <sheet name="GeneralReviewForm_v" sheetId="36" r:id="rId20"/>
+    <sheet name="Contacts" sheetId="41" r:id="rId21"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="152">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -492,6 +493,9 @@
   </si>
   <si>
     <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Automation Program For Test</t>
   </si>
 </sst>
 </file>
@@ -949,6 +953,108 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BADE6FB-E965-4263-BE22-5F02F8843366}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{531E32A4-7E13-4409-95B5-698B0506DEBB}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1039,7 +1145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5034D7D-3DCC-4A67-A25F-FCA9FE48CDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1082,7 +1188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70638D0A-5B68-4E82-8E59-C902079F733A}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1228,7 +1334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88D2545-36F8-47CF-B9C1-1EF7F48C6F22}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1298,7 +1404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CB8E10-5A8B-4AF3-AF66-F1E9AA7C9BBC}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1401,7 +1507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEB37B-B28E-4F60-BECB-CD35E74B4C36}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1558,7 +1664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82865F4C-F847-4F90-8B11-C831BFCC23C2}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1638,7 +1744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDAC24B-DC90-49E6-BD31-6F210026CA6D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1696,7 +1802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F7845C-214C-4C02-A5F4-6F38FB46E35D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1791,130 +1897,6 @@
       </c>
       <c r="C8" t="s">
         <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE64D93B-66B6-48F6-99BC-E4BA23590E06}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2015,6 +1997,130 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE64D93B-66B6-48F6-99BC-E4BA23590E06}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC7C533-9694-4FF8-A93E-689ECBD164CC}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2198,6 +2304,101 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C55F0F-09E3-4399-ADEA-7BEF752AF674}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.90625" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" tooltip="https://test7-internal.my.salesforce.com/00e0b000001fm3y" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{EAB7F9C6-7CE2-4ABE-9530-2AFE2C6A342E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03E8B95-40CB-49F7-AF29-3A2B27B21A61}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2258,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C485CB82-74B9-4E1E-9CE3-715999920922}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2301,7 +2502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19EA7F8-0885-4456-A6E5-96AB05BF51FA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2360,7 +2561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0E25E5-8973-4E31-A3CE-0B2930FA70C8}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2408,7 +2609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B47C19A-7081-4532-8CD1-2D1BC531686A}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2563,106 +2764,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BADE6FB-E965-4263-BE22-5F02F8843366}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8">
-        <v>10000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2987F7-DF88-4F96-B652-EE42963446B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5893093B-D396-453F-9DB4-EA3EFA68D31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="19" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="SiteVisitEdition_v" sheetId="35" r:id="rId19"/>
     <sheet name="GeneralReviewForm_v" sheetId="36" r:id="rId20"/>
     <sheet name="Contacts" sheetId="41" r:id="rId21"/>
+    <sheet name="ContactCreation" sheetId="43" r:id="rId22"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="169">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -496,6 +497,57 @@
   </si>
   <si>
     <t>Automation Program For Test</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>Automation Runtime Contact</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>AutomationManager@yopmail.com</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>SterlingUSA</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>MobilePhone</t>
+  </si>
+  <si>
+    <t>ProjectRole__c</t>
+  </si>
+  <si>
+    <t>fieldMailingStreet</t>
+  </si>
+  <si>
+    <t>MH</t>
   </si>
 </sst>
 </file>
@@ -558,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -580,6 +632,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2208,6 +2263,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB8C3BA-E383-402A-AD87-FB992F14A5E1}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="38.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7856789209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10">
+        <v>20171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{C8AC352D-35A2-405F-982E-3B7FAF90C7BD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E83D430-2DDF-4C96-A733-8F6A18593E6C}">
   <dimension ref="A1:C7"/>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5893093B-D396-453F-9DB4-EA3EFA68D31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42054CAB-0F2B-4960-B442-0DB683FFFBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="19" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>

--- a/src/main/resources/Program_Field_Values_PATCH.xlsx
+++ b/src/main/resources/Program_Field_Values_PATCH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42054CAB-0F2B-4960-B442-0DB683FFFBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6D4025-040E-4FBC-A1C7-4A9CBB1C2117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="167">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -464,12 +464,6 @@
   </si>
   <si>
     <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>PREG</t>
   </si>
   <si>
     <t>WebsiteAddress__c</t>
@@ -2288,10 +2282,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2299,10 +2293,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2310,10 +2304,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2321,7 +2315,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" s="10">
         <v>7856789209</v>
@@ -2332,10 +2326,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2343,10 +2337,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2354,10 +2348,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -2365,10 +2359,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -2376,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10">
         <v>20171</v>
@@ -2387,10 +2381,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2423,7 @@
         <v>62</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2437,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -2448,10 +2442,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2459,7 +2453,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
@@ -2525,7 +2519,7 @@
         <v>62</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2533,7 +2527,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -2544,10 +2538,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2555,7 +2549,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
@@ -2593,7 +2587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03E8B95-40CB-49F7-AF29-3A2B27B21A61}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
@@ -2618,7 +2612,7 @@
       <c r="B2" t="s">
         <v>141</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2629,24 +2623,13 @@
       <c r="B3" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{A65FC117-5B28-4005-829D-DA7C1A37EFC5}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{A65FC117-5B28-4005-829D-DA7C1A37EFC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
